--- a/backtest_runs/20260410_193731/filter/BATA/BATA.xlsx
+++ b/backtest_runs/20260410_193731/filter/BATA/BATA.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -584,10 +584,10 @@
         </is>
       </c>
       <c r="I3" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>100000</v>
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>100000</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>100000</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>100000</v>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>100000</v>
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="I15" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>100000</v>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>100000</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>100000</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>100000</v>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>100000</v>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="I21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>100000</v>
